--- a/data/teams.xlsx
+++ b/data/teams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28627"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jly26/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23865\Downloads\SKY (1)\SKY PROJECT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{CB5F2711-317E-F243-A823-8A86A16FCF75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17280" yWindow="760" windowWidth="17280" windowHeight="20380" xr2:uid="{0D28BA2C-DA9E-554B-9930-8DF19136572E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0D28BA2C-DA9E-554B-9930-8DF19136572E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1525,5361 +1525,3351 @@
           </cell>
         </row>
         <row r="3">
-          <cell r="A3" t="str">
-            <v>Joao Afonso</v>
-          </cell>
           <cell r="B3" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="A4" t="str">
-            <v>José Pacheco</v>
-          </cell>
           <cell r="B4" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="A5" t="str">
-            <v>João Campinhos</v>
-          </cell>
           <cell r="B5" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="A6" t="str">
-            <v>Carina Gomes</v>
-          </cell>
           <cell r="B6" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="7">
-          <cell r="A7" t="str">
-            <v>Francisco Sousa</v>
-          </cell>
           <cell r="B7" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="8">
-          <cell r="A8" t="str">
-            <v>João Achando</v>
-          </cell>
           <cell r="B8" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="9">
-          <cell r="A9" t="str">
-            <v>Leandro Mendes</v>
-          </cell>
           <cell r="B9" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="10">
-          <cell r="A10" t="str">
-            <v>Miguel Teixeira</v>
-          </cell>
           <cell r="B10" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="11">
-          <cell r="A11" t="str">
-            <v>Rui Tavares</v>
-          </cell>
           <cell r="B11" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="12">
-          <cell r="A12" t="str">
-            <v>Afonso Guerra</v>
-          </cell>
           <cell r="B12" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="13">
-          <cell r="A13" t="str">
-            <v>Rafael Lourenço</v>
-          </cell>
           <cell r="B13" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="14">
-          <cell r="A14" t="str">
-            <v>Alexandre Vilão</v>
-          </cell>
           <cell r="B14" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="15">
-          <cell r="A15" t="str">
-            <v>André Marinho</v>
-          </cell>
           <cell r="B15" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="A16" t="str">
-            <v>Igor Silva</v>
-          </cell>
           <cell r="B16" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="A17" t="str">
-            <v>Paulo Campos</v>
-          </cell>
           <cell r="B17" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="18">
-          <cell r="A18" t="str">
-            <v>Pedro Durães</v>
-          </cell>
           <cell r="B18" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="19">
-          <cell r="A19" t="str">
-            <v>Guilherme Teixeira</v>
-          </cell>
           <cell r="B19" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="20">
-          <cell r="A20" t="str">
-            <v>Nuno Cruz</v>
-          </cell>
           <cell r="B20" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="21">
-          <cell r="A21" t="str">
-            <v>Bernardo Guerreiro</v>
-          </cell>
           <cell r="B21" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="22">
-          <cell r="A22" t="str">
-            <v>Daniela Levezinho</v>
-          </cell>
           <cell r="B22" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="23">
-          <cell r="A23" t="str">
-            <v>Diego Nascimento</v>
-          </cell>
           <cell r="B23" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="24">
-          <cell r="A24" t="str">
-            <v>Pedro Lima e Silva</v>
-          </cell>
           <cell r="B24" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="25">
-          <cell r="A25" t="str">
-            <v>Sanjay Purswani</v>
-          </cell>
           <cell r="B25" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="26">
-          <cell r="A26" t="str">
-            <v>Célia Cunha</v>
-          </cell>
           <cell r="B26" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="A27" t="str">
-            <v>Miguel Rodrigues</v>
-          </cell>
           <cell r="B27" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="28">
-          <cell r="A28" t="str">
-            <v>Hugo Rita</v>
-          </cell>
           <cell r="B28" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="29">
-          <cell r="A29" t="str">
-            <v>João Ricardo Gomes</v>
-          </cell>
           <cell r="B29" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="30">
-          <cell r="A30" t="str">
-            <v>Miguel Borges</v>
-          </cell>
           <cell r="B30" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="31">
-          <cell r="A31" t="str">
-            <v>Pedro Daniel Sousa</v>
-          </cell>
           <cell r="B31" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="32">
-          <cell r="A32" t="str">
-            <v>Alexandre Dias</v>
-          </cell>
           <cell r="B32" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="33">
-          <cell r="A33" t="str">
-            <v>Hortência Silva</v>
-          </cell>
           <cell r="B33" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="34">
-          <cell r="A34" t="str">
-            <v>Cristina Mendes</v>
-          </cell>
           <cell r="B34" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="35">
-          <cell r="A35" t="str">
-            <v>Michal Topinka</v>
-          </cell>
           <cell r="B35" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="36">
-          <cell r="A36" t="str">
-            <v>Petro Fesiuk</v>
-          </cell>
           <cell r="B36" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="37">
-          <cell r="A37" t="str">
-            <v>Jan Molnár</v>
-          </cell>
           <cell r="B37" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="38">
-          <cell r="A38" t="str">
-            <v>Dmitry Kuznetsov</v>
-          </cell>
           <cell r="B38" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="39">
-          <cell r="A39" t="str">
-            <v>Kamil Zajac</v>
-          </cell>
           <cell r="B39" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="40">
-          <cell r="A40" t="str">
-            <v>Richard Zakl</v>
-          </cell>
           <cell r="B40" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="41">
-          <cell r="A41" t="str">
-            <v>Pavel Popp</v>
-          </cell>
           <cell r="B41" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="42">
-          <cell r="A42" t="str">
-            <v>Richard Tinner</v>
-          </cell>
           <cell r="B42" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="43">
-          <cell r="A43" t="str">
-            <v>Edgar Ribeiro</v>
-          </cell>
           <cell r="B43" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="44">
-          <cell r="A44" t="str">
-            <v>David Rooks</v>
-          </cell>
           <cell r="B44" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="45">
-          <cell r="A45" t="str">
-            <v>Ernest Wiafe-Annor</v>
-          </cell>
           <cell r="B45" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="46">
-          <cell r="A46" t="str">
-            <v>Abhiram S</v>
-          </cell>
           <cell r="B46" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="47">
-          <cell r="A47" t="str">
-            <v>Jakub Svihla</v>
-          </cell>
           <cell r="B47" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="48">
-          <cell r="A48" t="str">
-            <v>Kadeeja Bai</v>
-          </cell>
           <cell r="B48" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="49">
-          <cell r="A49" t="str">
-            <v>Kevo Thomson</v>
-          </cell>
           <cell r="B49" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="50">
-          <cell r="A50" t="str">
-            <v>Le Le Wang-Riches</v>
-          </cell>
           <cell r="B50" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="51">
-          <cell r="A51" t="str">
-            <v>Ricardo Afonso</v>
-          </cell>
           <cell r="B51" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="52">
-          <cell r="A52" t="str">
-            <v>Suraj Kalsi</v>
-          </cell>
           <cell r="B52" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="53">
-          <cell r="A53" t="str">
-            <v>Ali Syed</v>
-          </cell>
           <cell r="B53" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="54">
-          <cell r="A54" t="str">
-            <v>Patrick Harris</v>
-          </cell>
           <cell r="B54" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="55">
-          <cell r="A55" t="str">
-            <v>Edgar Kiljak</v>
-          </cell>
           <cell r="B55" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="56">
-          <cell r="A56" t="str">
-            <v>Habib Karim</v>
-          </cell>
           <cell r="B56" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="57">
-          <cell r="A57" t="str">
-            <v>Kaushalya Sandamali</v>
-          </cell>
           <cell r="B57" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="58">
-          <cell r="A58" t="str">
-            <v>Reio Laabus</v>
-          </cell>
           <cell r="B58" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="59">
-          <cell r="A59" t="str">
-            <v>Stoyan Garov</v>
-          </cell>
           <cell r="B59" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="60">
-          <cell r="A60" t="str">
-            <v>Nathan Melly</v>
-          </cell>
           <cell r="B60" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="61">
-          <cell r="A61" t="str">
-            <v>Aaron Agnew-Griffith</v>
-          </cell>
           <cell r="B61" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="62">
-          <cell r="A62" t="str">
-            <v>Madhura Naveen</v>
-          </cell>
           <cell r="B62" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="63">
-          <cell r="A63" t="str">
-            <v>Ricardo Cacheira</v>
-          </cell>
           <cell r="B63" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="64">
-          <cell r="A64" t="str">
-            <v>Joseph Noakes</v>
-          </cell>
           <cell r="B64" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="65">
-          <cell r="A65" t="str">
-            <v>Hugo Dias</v>
-          </cell>
           <cell r="B65" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="66">
-          <cell r="A66" t="str">
-            <v>Alexandre Heleno</v>
-          </cell>
           <cell r="B66" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="67">
-          <cell r="A67" t="str">
-            <v>Bruna Esteves</v>
-          </cell>
           <cell r="B67" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="68">
-          <cell r="A68" t="str">
-            <v>Nuno Castro</v>
-          </cell>
           <cell r="B68" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="69">
-          <cell r="A69" t="str">
-            <v>Rafael Castro</v>
-          </cell>
           <cell r="B69" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="70">
-          <cell r="A70" t="str">
-            <v>Rui Barbosa</v>
-          </cell>
           <cell r="B70" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="71">
-          <cell r="A71" t="str">
-            <v>Rudney Neto</v>
-          </cell>
           <cell r="B71" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="72">
-          <cell r="A72" t="str">
-            <v>Hazik Anwar</v>
-          </cell>
           <cell r="B72" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="73">
-          <cell r="A73" t="str">
-            <v>Simon Morris</v>
-          </cell>
           <cell r="B73" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="74">
-          <cell r="A74" t="str">
-            <v>Rachana Mudrakolla</v>
-          </cell>
           <cell r="B74" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="75">
-          <cell r="A75" t="str">
-            <v>Pedro Raposo</v>
-          </cell>
           <cell r="B75" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="76">
-          <cell r="A76" t="str">
-            <v>Gurpreet Mahi</v>
-          </cell>
           <cell r="B76" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="77">
-          <cell r="A77" t="str">
-            <v>Bruno Grácio</v>
-          </cell>
           <cell r="B77" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="78">
-          <cell r="A78" t="str">
-            <v>Francisco Ludovico</v>
-          </cell>
           <cell r="B78" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="79">
-          <cell r="A79" t="str">
-            <v>André Gomes</v>
-          </cell>
           <cell r="B79" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="80">
-          <cell r="A80" t="str">
-            <v>Luís Mestre</v>
-          </cell>
           <cell r="B80" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="81">
-          <cell r="A81" t="str">
-            <v>Tufail Rahman</v>
-          </cell>
           <cell r="B81" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="82">
-          <cell r="A82" t="str">
-            <v>Erki Luik</v>
-          </cell>
           <cell r="B82" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="83">
-          <cell r="A83" t="str">
-            <v>Alistair Moore</v>
-          </cell>
           <cell r="B83" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="84">
-          <cell r="A84" t="str">
-            <v>Luca Borrione</v>
-          </cell>
           <cell r="B84" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="85">
-          <cell r="A85" t="str">
-            <v>Seb Flippence</v>
-          </cell>
           <cell r="B85" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="86">
-          <cell r="A86" t="str">
-            <v>Bernardo Brandão</v>
-          </cell>
           <cell r="B86" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="87">
-          <cell r="A87" t="str">
-            <v>Paul Lanigan</v>
-          </cell>
           <cell r="B87" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="88">
-          <cell r="A88" t="str">
-            <v>João Beltrão</v>
-          </cell>
           <cell r="B88" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="89">
-          <cell r="A89" t="str">
-            <v>João Carias</v>
-          </cell>
           <cell r="B89" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="90">
-          <cell r="A90" t="str">
-            <v>Bruno Assunção</v>
-          </cell>
           <cell r="B90" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="91">
-          <cell r="A91" t="str">
-            <v>Zaeem Qadeer</v>
-          </cell>
           <cell r="B91" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="92">
-          <cell r="A92" t="str">
-            <v>Jonathan Miller</v>
-          </cell>
           <cell r="B92" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="93">
-          <cell r="A93" t="str">
-            <v>Jayesh Mistry</v>
-          </cell>
           <cell r="B93" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="94">
-          <cell r="A94" t="str">
-            <v>Harry Downing</v>
-          </cell>
           <cell r="B94" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="95">
-          <cell r="A95" t="str">
-            <v>Fabiane Pelucio</v>
-          </cell>
           <cell r="B95" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="96">
-          <cell r="A96" t="str">
-            <v>Sharda Mahindra</v>
-          </cell>
           <cell r="B96" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="97">
-          <cell r="A97" t="str">
-            <v>Anish Phillip</v>
-          </cell>
           <cell r="B97" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="98">
-          <cell r="A98" t="str">
-            <v xml:space="preserve">Martin Šuráb      </v>
-          </cell>
           <cell r="B98" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="99">
-          <cell r="A99" t="str">
-            <v>Petr Introvič</v>
-          </cell>
           <cell r="B99" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="100">
-          <cell r="A100" t="str">
-            <v>Jakub Brož</v>
-          </cell>
           <cell r="B100" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="101">
-          <cell r="A101" t="str">
-            <v>Tomáš Stolařík</v>
-          </cell>
           <cell r="B101" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="102">
-          <cell r="A102" t="str">
-            <v>Vojtech Zalesky</v>
-          </cell>
           <cell r="B102" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="103">
-          <cell r="A103" t="str">
-            <v>Alena Bartonová</v>
-          </cell>
           <cell r="B103" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="104">
-          <cell r="A104" t="str">
-            <v>Pedro Fernandes</v>
-          </cell>
           <cell r="B104" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="105">
-          <cell r="A105" t="str">
-            <v>Diogo Peres</v>
-          </cell>
           <cell r="B105" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="106">
-          <cell r="A106" t="str">
-            <v>Guilherme Simões</v>
-          </cell>
           <cell r="B106" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="107">
-          <cell r="A107" t="str">
-            <v>Jorge Graça</v>
-          </cell>
           <cell r="B107" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="108">
-          <cell r="A108" t="str">
-            <v>Rodrigo Moura</v>
-          </cell>
           <cell r="B108" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="109">
-          <cell r="A109" t="str">
-            <v>Ricardo Fonseca</v>
-          </cell>
           <cell r="B109" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="110">
-          <cell r="A110" t="str">
-            <v>Christof Brütsch</v>
-          </cell>
           <cell r="B110" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="111">
-          <cell r="A111" t="str">
-            <v>Malcom Smy</v>
-          </cell>
           <cell r="B111" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="112">
-          <cell r="A112" t="str">
-            <v>Ricardo Castelhano</v>
-          </cell>
           <cell r="B112" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="113">
-          <cell r="A113" t="str">
-            <v>Helder Marques</v>
-          </cell>
           <cell r="B113" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="114">
-          <cell r="A114" t="str">
-            <v>Inês Chagas</v>
-          </cell>
           <cell r="B114" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="115">
-          <cell r="A115" t="str">
-            <v>João Matos</v>
-          </cell>
           <cell r="B115" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="116">
-          <cell r="A116" t="str">
-            <v>Manuela Cardoso</v>
-          </cell>
           <cell r="B116" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="117">
-          <cell r="A117" t="str">
-            <v>Miguel Bastos</v>
-          </cell>
           <cell r="B117" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="118">
-          <cell r="A118" t="str">
-            <v>Venkatesh Kommineni</v>
-          </cell>
           <cell r="B118" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="119">
-          <cell r="A119" t="str">
-            <v>Ana Santos</v>
-          </cell>
           <cell r="B119" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="120">
-          <cell r="A120" t="str">
-            <v>Brindha Natarajan</v>
-          </cell>
           <cell r="B120" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="121">
-          <cell r="A121" t="str">
-            <v>João Pereira</v>
-          </cell>
           <cell r="B121" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="122">
-          <cell r="A122" t="str">
-            <v>Gonçalo Gomes</v>
-          </cell>
           <cell r="B122" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="123">
-          <cell r="A123" t="str">
-            <v>Mário Vieira</v>
-          </cell>
           <cell r="B123" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="124">
-          <cell r="A124" t="str">
-            <v>Carlos Baptista</v>
-          </cell>
           <cell r="B124" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="125">
-          <cell r="A125" t="str">
-            <v>Gonçalo Assunção</v>
-          </cell>
           <cell r="B125" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="126">
-          <cell r="A126" t="str">
-            <v>João Francisco Silva</v>
-          </cell>
           <cell r="B126" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="127">
-          <cell r="A127" t="str">
-            <v>Matilde Ribeiro</v>
-          </cell>
           <cell r="B127" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="128">
-          <cell r="A128" t="str">
-            <v>Eliana Barros</v>
-          </cell>
           <cell r="B128" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="129">
-          <cell r="A129" t="str">
-            <v>Tomas Zeman</v>
-          </cell>
           <cell r="B129" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="130">
-          <cell r="A130" t="str">
-            <v>Beatriz Rosa</v>
-          </cell>
           <cell r="B130" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="131">
-          <cell r="A131" t="str">
-            <v>Alice Fernandes</v>
-          </cell>
           <cell r="B131" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="132">
-          <cell r="A132" t="str">
-            <v>Ana Alves</v>
-          </cell>
           <cell r="B132" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="133">
-          <cell r="A133" t="str">
-            <v>Manuel Cardoso</v>
-          </cell>
           <cell r="B133" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="134">
-          <cell r="A134" t="str">
-            <v>Šimon Maresz</v>
-          </cell>
           <cell r="B134" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="135">
-          <cell r="A135" t="str">
-            <v>Jakub Kratěna</v>
-          </cell>
           <cell r="B135" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="136">
-          <cell r="A136" t="str">
-            <v>Václav  Beneš</v>
-          </cell>
           <cell r="B136" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="137">
-          <cell r="A137" t="str">
-            <v>João Lourenço</v>
-          </cell>
           <cell r="B137" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="138">
-          <cell r="A138" t="str">
-            <v>Anastasiya Koňaková</v>
-          </cell>
           <cell r="B138" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="139">
-          <cell r="A139" t="str">
-            <v>Carlos Timóteo</v>
-          </cell>
           <cell r="B139" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="140">
-          <cell r="A140" t="str">
-            <v>Nuno Jesus</v>
-          </cell>
           <cell r="B140" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="141">
-          <cell r="A141" t="str">
-            <v>Flávio Caria</v>
-          </cell>
           <cell r="B141" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="142">
-          <cell r="A142" t="str">
-            <v>Nuno Correia</v>
-          </cell>
           <cell r="B142" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="143">
-          <cell r="A143" t="str">
-            <v xml:space="preserve">Filipe Pereira </v>
-          </cell>
           <cell r="B143" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="144">
-          <cell r="A144" t="str">
-            <v>Mandeep Khataria</v>
-          </cell>
           <cell r="B144" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="145">
-          <cell r="A145" t="str">
-            <v>Shahab Saeeda</v>
-          </cell>
           <cell r="B145" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="146">
-          <cell r="A146" t="str">
-            <v>Alexander Plummer</v>
-          </cell>
           <cell r="B146" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="147">
-          <cell r="A147" t="str">
-            <v>Rupesh Bhatti</v>
-          </cell>
           <cell r="B147" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="148">
-          <cell r="A148" t="str">
-            <v>Joe Oliver</v>
-          </cell>
           <cell r="B148" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="149">
-          <cell r="A149" t="str">
-            <v>Tom Bakker</v>
-          </cell>
           <cell r="B149" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="150">
-          <cell r="A150" t="str">
-            <v>Yash Ghelani</v>
-          </cell>
           <cell r="B150" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="151">
-          <cell r="A151" t="str">
-            <v>Zubair Gaj</v>
-          </cell>
           <cell r="B151" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="152">
-          <cell r="A152" t="str">
-            <v>David Dossou</v>
-          </cell>
           <cell r="B152" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="153">
-          <cell r="A153" t="str">
-            <v>Aamun Malhotra</v>
-          </cell>
           <cell r="B153" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="154">
-          <cell r="A154" t="str">
-            <v>Emad Ahmed</v>
-          </cell>
           <cell r="B154" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="155">
-          <cell r="A155" t="str">
-            <v>Sandra Almeida</v>
-          </cell>
           <cell r="B155" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="156">
-          <cell r="A156" t="str">
-            <v>Frederico Rivera Ferreira</v>
-          </cell>
           <cell r="B156" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="157">
-          <cell r="A157" t="str">
-            <v>Francisco Caldeira</v>
-          </cell>
           <cell r="B157" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="158">
-          <cell r="A158" t="str">
-            <v>Ricardo Francisco Simoes</v>
-          </cell>
           <cell r="B158" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="159">
-          <cell r="A159" t="str">
-            <v>Ricardo Gordo</v>
-          </cell>
           <cell r="B159" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="160">
-          <cell r="A160" t="str">
-            <v>Sónia Pereira</v>
-          </cell>
           <cell r="B160" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="161">
-          <cell r="A161" t="str">
-            <v>Andrei Patricio</v>
-          </cell>
           <cell r="B161" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="162">
-          <cell r="A162" t="str">
-            <v>Daniel Cabaça</v>
-          </cell>
           <cell r="B162" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="163">
-          <cell r="A163" t="str">
-            <v>Ricardo Tavares</v>
-          </cell>
           <cell r="B163" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="164">
-          <cell r="A164" t="str">
-            <v>Bruno Teixeira</v>
-          </cell>
           <cell r="B164" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="165">
-          <cell r="A165" t="str">
-            <v>Fábio Sá</v>
-          </cell>
           <cell r="B165" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="166">
-          <cell r="A166" t="str">
-            <v>João Rodrigues</v>
-          </cell>
           <cell r="B166" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="167">
-          <cell r="A167" t="str">
-            <v>Miguel Marcos</v>
-          </cell>
           <cell r="B167" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="168">
-          <cell r="A168" t="str">
-            <v>Nuno Vinagre</v>
-          </cell>
           <cell r="B168" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="169">
-          <cell r="A169" t="str">
-            <v>Crowdtesting</v>
-          </cell>
           <cell r="B169" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="170">
-          <cell r="A170" t="str">
-            <v>Crowdtesting</v>
-          </cell>
           <cell r="B170" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="171">
-          <cell r="A171" t="str">
-            <v>Juliana Rossoni</v>
-          </cell>
           <cell r="B171" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="172">
-          <cell r="A172" t="str">
-            <v>Veronika Synieokaia</v>
-          </cell>
           <cell r="B172" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="173">
-          <cell r="A173" t="str">
-            <v>Mikhail Nizevich</v>
-          </cell>
           <cell r="B173" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="174">
-          <cell r="A174" t="str">
-            <v>Cíntia Teles</v>
-          </cell>
           <cell r="B174" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="175">
-          <cell r="A175" t="str">
-            <v>Telma Duarte</v>
-          </cell>
           <cell r="B175" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="176">
-          <cell r="A176" t="str">
-            <v>Afonso Silva</v>
-          </cell>
           <cell r="B176" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="177">
-          <cell r="A177" t="str">
-            <v>Rekha Thalla</v>
-          </cell>
           <cell r="B177" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="178">
-          <cell r="A178" t="str">
-            <v>Aditiya Rohilla</v>
-          </cell>
           <cell r="B178" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="179">
-          <cell r="A179" t="str">
-            <v>Aaron Sudhera</v>
-          </cell>
           <cell r="B179" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="180">
-          <cell r="A180" t="str">
-            <v>Anil Sathish</v>
-          </cell>
           <cell r="B180" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="181">
-          <cell r="A181" t="str">
-            <v>Sheshank Jonnalagadla</v>
-          </cell>
           <cell r="B181" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="182">
-          <cell r="A182" t="str">
-            <v>João Francisco Pereira</v>
-          </cell>
           <cell r="B182" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="183">
-          <cell r="A183" t="str">
-            <v>Ana Calção</v>
-          </cell>
           <cell r="B183" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="184">
-          <cell r="A184" t="str">
-            <v>Patrick Guilherme</v>
-          </cell>
           <cell r="B184" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="185">
-          <cell r="A185" t="str">
-            <v>Muneer Shaik</v>
-          </cell>
           <cell r="B185" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="186">
-          <cell r="A186" t="str">
-            <v>Puneeth Reddy</v>
-          </cell>
           <cell r="B186" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="187">
-          <cell r="A187" t="str">
-            <v>Crowdtesting</v>
-          </cell>
           <cell r="B187" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="188">
-          <cell r="A188" t="str">
-            <v>Crowdtesting</v>
-          </cell>
           <cell r="B188" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="189">
-          <cell r="A189" t="str">
-            <v>George Hill</v>
-          </cell>
           <cell r="B189" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="190">
-          <cell r="A190" t="str">
-            <v>Liam O'Sullivan</v>
-          </cell>
           <cell r="B190" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="191">
-          <cell r="A191" t="str">
-            <v>Martin Oppetit</v>
-          </cell>
           <cell r="B191" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="192">
-          <cell r="A192" t="str">
-            <v>Lester Pais</v>
-          </cell>
           <cell r="B192" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="193">
-          <cell r="A193" t="str">
-            <v>Celso Fernandes</v>
-          </cell>
           <cell r="B193" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="194">
-          <cell r="A194" t="str">
-            <v>Mário Teixeira</v>
-          </cell>
           <cell r="B194" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="195">
-          <cell r="A195" t="str">
-            <v>Nuno Potier</v>
-          </cell>
           <cell r="B195" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="196">
-          <cell r="A196" t="str">
-            <v>Paulo Ferreira</v>
-          </cell>
           <cell r="B196" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="197">
-          <cell r="A197" t="str">
-            <v>Elizeu Cuginguilua</v>
-          </cell>
           <cell r="B197" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="198">
-          <cell r="A198" t="str">
-            <v>Pedro Ribeiro</v>
-          </cell>
           <cell r="B198" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="199">
-          <cell r="A199" t="str">
-            <v>Dayam Javed</v>
-          </cell>
           <cell r="B199" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="200">
-          <cell r="A200" t="str">
-            <v>Pawel Hertman</v>
-          </cell>
           <cell r="B200" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="201">
-          <cell r="A201" t="str">
-            <v>Jonathan Morgan</v>
-          </cell>
           <cell r="B201" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="202">
-          <cell r="A202" t="str">
-            <v>Rúben Freitas</v>
-          </cell>
           <cell r="B202" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="203">
-          <cell r="A203" t="str">
-            <v>Joana Ferreira</v>
-          </cell>
           <cell r="B203" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="204">
-          <cell r="A204" t="str">
-            <v>Fehmida Medlock</v>
-          </cell>
           <cell r="B204" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="205">
-          <cell r="A205" t="str">
-            <v>Marcin Kulwikowski</v>
-          </cell>
           <cell r="B205" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="206">
-          <cell r="A206" t="str">
-            <v>Jean Barbosa</v>
-          </cell>
           <cell r="B206" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="207">
-          <cell r="A207" t="str">
-            <v>Nuno Santos</v>
-          </cell>
           <cell r="B207" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="208">
-          <cell r="A208" t="str">
-            <v>Tiago Garcia</v>
-          </cell>
           <cell r="B208" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="209">
-          <cell r="A209" t="str">
-            <v>Heike Waap</v>
-          </cell>
           <cell r="B209" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="210">
-          <cell r="A210" t="str">
-            <v>Luís Soares</v>
-          </cell>
           <cell r="B210" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="211">
-          <cell r="A211" t="str">
-            <v>Paulo Santos</v>
-          </cell>
           <cell r="B211" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="212">
-          <cell r="A212" t="str">
-            <v>Daria Kondratenok</v>
-          </cell>
           <cell r="B212" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="213">
-          <cell r="A213" t="str">
-            <v>Igor Sousa</v>
-          </cell>
           <cell r="B213" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="214">
-          <cell r="A214" t="str">
-            <v>Dany Silva</v>
-          </cell>
           <cell r="B214" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="215">
-          <cell r="A215" t="str">
-            <v>Eduardo Vasconcelos</v>
-          </cell>
           <cell r="B215" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="216">
-          <cell r="A216" t="str">
-            <v>Élton Gouveia</v>
-          </cell>
           <cell r="B216" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="217">
-          <cell r="A217" t="str">
-            <v>Tomás Ornelas</v>
-          </cell>
           <cell r="B217" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="218">
-          <cell r="A218" t="str">
-            <v>Tomasz Rejment</v>
-          </cell>
           <cell r="B218" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="219">
-          <cell r="A219" t="str">
-            <v>Tiago Miguel Correia</v>
-          </cell>
           <cell r="B219" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="220">
-          <cell r="A220" t="str">
-            <v>Moin Ahmed</v>
-          </cell>
           <cell r="B220" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="221">
-          <cell r="A221" t="str">
-            <v>Anish Shah</v>
-          </cell>
           <cell r="B221" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="222">
-          <cell r="A222" t="str">
-            <v>Adnan Babar</v>
-          </cell>
           <cell r="B222" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="223">
-          <cell r="A223" t="str">
-            <v>Davide Longo</v>
-          </cell>
           <cell r="B223" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="224">
-          <cell r="A224" t="str">
-            <v>Patryk Seredynski</v>
-          </cell>
           <cell r="B224" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="225">
-          <cell r="A225" t="str">
-            <v>Gokul Madhavan</v>
-          </cell>
           <cell r="B225" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="226">
-          <cell r="A226" t="str">
-            <v>Michael Stone</v>
-          </cell>
           <cell r="B226" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="227">
-          <cell r="A227" t="str">
-            <v>Mallika Kapoor</v>
-          </cell>
           <cell r="B227" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="228">
-          <cell r="A228" t="str">
-            <v>Elle Ordona</v>
-          </cell>
           <cell r="B228" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="229">
-          <cell r="A229" t="str">
-            <v>Adebola Aladesuru</v>
-          </cell>
           <cell r="B229" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="230">
-          <cell r="A230" t="str">
-            <v>Albert Bosch</v>
-          </cell>
           <cell r="B230" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="231">
-          <cell r="A231" t="str">
-            <v>Elena Luna Amiano</v>
-          </cell>
           <cell r="B231" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="232">
-          <cell r="A232" t="str">
-            <v>Russell Sherwood</v>
-          </cell>
           <cell r="B232" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="233">
-          <cell r="A233" t="str">
-            <v>Sandeep sethi</v>
-          </cell>
           <cell r="B233" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="234">
-          <cell r="A234" t="str">
-            <v>Chitra Mali</v>
-          </cell>
           <cell r="B234" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="235">
-          <cell r="A235" t="str">
-            <v>Alexandre Resende</v>
-          </cell>
           <cell r="B235" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="236">
-          <cell r="A236" t="str">
-            <v>Danilo Casassa</v>
-          </cell>
           <cell r="B236" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="237">
-          <cell r="A237" t="str">
-            <v>Lee Burgess</v>
-          </cell>
           <cell r="B237" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="238">
-          <cell r="A238" t="str">
-            <v>Rita Silva</v>
-          </cell>
           <cell r="B238" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="239">
-          <cell r="A239" t="str">
-            <v>Jaqueline Pereira</v>
-          </cell>
           <cell r="B239" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="240">
-          <cell r="A240" t="str">
-            <v>Crowdtesting</v>
-          </cell>
           <cell r="B240" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="241">
-          <cell r="A241" t="str">
-            <v>Crowdtesting</v>
-          </cell>
           <cell r="B241" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="242">
-          <cell r="A242" t="str">
-            <v>ANDRE SILVA</v>
-          </cell>
           <cell r="B242" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="243">
-          <cell r="A243" t="str">
-            <v>Francisco Gonçalves</v>
-          </cell>
           <cell r="B243" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="244">
-          <cell r="A244" t="str">
-            <v>Gonçalo Antunes</v>
-          </cell>
           <cell r="B244" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="245">
-          <cell r="A245" t="str">
-            <v>Tiago Pestana</v>
-          </cell>
           <cell r="B245" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="246">
-          <cell r="A246" t="str">
-            <v>Victor Tavernari</v>
-          </cell>
           <cell r="B246" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="247">
-          <cell r="A247" t="str">
-            <v>Ricardo Barroso</v>
-          </cell>
           <cell r="B247" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="248">
-          <cell r="A248" t="str">
-            <v>Fábio Bernardo</v>
-          </cell>
           <cell r="B248" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="249">
-          <cell r="A249" t="str">
-            <v>Carlos Martins</v>
-          </cell>
           <cell r="B249" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="250">
-          <cell r="A250" t="str">
-            <v>Francisco Suarez</v>
-          </cell>
           <cell r="B250" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="251">
-          <cell r="A251" t="str">
-            <v>Robert Mooney</v>
-          </cell>
           <cell r="B251" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="252">
-          <cell r="A252" t="str">
-            <v>Wojciech Stasinski</v>
-          </cell>
           <cell r="B252" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="253">
-          <cell r="A253" t="str">
-            <v>Sara Costa</v>
-          </cell>
           <cell r="B253" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="254">
-          <cell r="A254" t="str">
-            <v>Pollyanna Giles</v>
-          </cell>
           <cell r="B254" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="255">
-          <cell r="A255" t="str">
-            <v>Younas Chentouf</v>
-          </cell>
           <cell r="B255" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="256">
-          <cell r="A256" t="str">
-            <v>Mohammad Butt</v>
-          </cell>
           <cell r="B256" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="257">
-          <cell r="A257" t="str">
-            <v>João NOT Gomes</v>
-          </cell>
           <cell r="B257" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="258">
-          <cell r="A258" t="str">
-            <v>Gonçalo Tavares</v>
-          </cell>
           <cell r="B258" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="259">
-          <cell r="A259" t="str">
-            <v>Pedro Nunes</v>
-          </cell>
           <cell r="B259" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="260">
-          <cell r="A260" t="str">
-            <v>Patrícia Leal</v>
-          </cell>
           <cell r="B260" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="261">
-          <cell r="A261" t="str">
-            <v>Tiago Rodrigues</v>
-          </cell>
           <cell r="B261" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="262">
-          <cell r="A262" t="str">
-            <v>Michelle Knevitz Portocarrero</v>
-          </cell>
           <cell r="B262" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="263">
-          <cell r="A263" t="str">
-            <v>António Jorge</v>
-          </cell>
           <cell r="B263" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="264">
-          <cell r="A264" t="str">
-            <v>Rodrigo Cruz</v>
-          </cell>
           <cell r="B264" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="265">
-          <cell r="A265" t="str">
-            <v>Miguel Ferreira</v>
-          </cell>
           <cell r="B265" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="266">
-          <cell r="A266" t="str">
-            <v>André Cravo</v>
-          </cell>
           <cell r="B266" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="267">
-          <cell r="A267" t="str">
-            <v>Cauã Santos</v>
-          </cell>
           <cell r="B267" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="268">
-          <cell r="A268" t="str">
-            <v>Robin Křenecký</v>
-          </cell>
           <cell r="B268" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="269">
-          <cell r="A269" t="str">
-            <v>Najeeb Rehman</v>
-          </cell>
           <cell r="B269" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="270">
-          <cell r="A270" t="str">
-            <v>Hélder Malícia</v>
-          </cell>
           <cell r="B270" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="271">
-          <cell r="A271" t="str">
-            <v>Ondřej Macoszek</v>
-          </cell>
           <cell r="B271" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="272">
-          <cell r="A272" t="str">
-            <v>Roman Auersvald</v>
-          </cell>
           <cell r="B272" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="273">
-          <cell r="A273" t="str">
-            <v>Artem Kanaurov</v>
-          </cell>
           <cell r="B273" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="274">
-          <cell r="A274" t="str">
-            <v>Alexander Grigoryev</v>
-          </cell>
           <cell r="B274" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="275">
-          <cell r="A275" t="str">
-            <v>Jaroslav Novak</v>
-          </cell>
           <cell r="B275" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="276">
-          <cell r="A276" t="str">
-            <v>Jakub Hrbek</v>
-          </cell>
           <cell r="B276" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="277">
-          <cell r="A277" t="str">
-            <v>Aasim Choudhary</v>
-          </cell>
           <cell r="B277" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="278">
-          <cell r="A278" t="str">
-            <v>Ommar Al Quisi</v>
-          </cell>
           <cell r="B278" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="279">
-          <cell r="A279" t="str">
-            <v>Emmanuel Kehinde</v>
-          </cell>
           <cell r="B279" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="280">
-          <cell r="A280" t="str">
-            <v>Nicholas DePontes</v>
-          </cell>
           <cell r="B280" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="281">
-          <cell r="A281" t="str">
-            <v>Alper Karatas</v>
-          </cell>
           <cell r="B281" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="282">
-          <cell r="A282" t="str">
-            <v>Andres Ramirez</v>
-          </cell>
           <cell r="B282" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="283">
-          <cell r="A283" t="str">
-            <v>Harrison Porter</v>
-          </cell>
           <cell r="B283" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="284">
-          <cell r="A284" t="str">
-            <v>Pranav Kasetti</v>
-          </cell>
           <cell r="B284" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="285">
-          <cell r="A285" t="str">
-            <v>Raaji Putcha</v>
-          </cell>
           <cell r="B285" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="286">
-          <cell r="A286" t="str">
-            <v>Ruhail Singh</v>
-          </cell>
           <cell r="B286" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="287">
-          <cell r="A287" t="str">
-            <v>Luís Gorgulho</v>
-          </cell>
           <cell r="B287" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="288">
-          <cell r="A288" t="str">
-            <v>Rama Sadineni</v>
-          </cell>
           <cell r="B288" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="289">
-          <cell r="A289" t="str">
-            <v>Aryele Oliveira</v>
-          </cell>
           <cell r="B289" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="290">
-          <cell r="A290" t="str">
-            <v>Inês Figueiredo</v>
-          </cell>
           <cell r="B290" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="291">
-          <cell r="A291" t="str">
-            <v>Mubeen Farooq</v>
-          </cell>
           <cell r="B291" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="292">
-          <cell r="A292" t="str">
-            <v>Mohammad Akhtar</v>
-          </cell>
           <cell r="B292" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="293">
-          <cell r="A293" t="str">
-            <v>Crowdtesting</v>
-          </cell>
           <cell r="B293" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="294">
-          <cell r="A294" t="str">
-            <v>Crowdtesting</v>
-          </cell>
           <cell r="B294" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="295">
-          <cell r="A295" t="str">
-            <v>Diego Valente</v>
-          </cell>
           <cell r="B295" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="296">
-          <cell r="A296" t="str">
-            <v>Miguel Batista</v>
-          </cell>
           <cell r="B296" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="297">
-          <cell r="A297" t="str">
-            <v>Arunabh Ankur</v>
-          </cell>
           <cell r="B297" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="298">
-          <cell r="A298" t="str">
-            <v>João Correia</v>
-          </cell>
           <cell r="B298" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="299">
-          <cell r="A299" t="str">
-            <v>Carlos Matos</v>
-          </cell>
           <cell r="B299" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="300">
-          <cell r="A300" t="str">
-            <v>Renato Ribeiro</v>
-          </cell>
           <cell r="B300" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="301">
-          <cell r="A301" t="str">
-            <v>Mariana Ramos</v>
-          </cell>
           <cell r="B301" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="302">
-          <cell r="A302" t="str">
-            <v>Renato Viana</v>
-          </cell>
           <cell r="B302" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="303">
-          <cell r="A303" t="str">
-            <v>Mariana Mendes</v>
-          </cell>
           <cell r="B303" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="304">
-          <cell r="A304" t="str">
-            <v>Paulo Cruz</v>
-          </cell>
           <cell r="B304" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="305">
-          <cell r="A305" t="str">
-            <v>Pedro Miguel Silva</v>
-          </cell>
           <cell r="B305" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="306">
-          <cell r="A306" t="str">
-            <v>Aníbal Alves</v>
-          </cell>
           <cell r="B306" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="307">
-          <cell r="A307" t="str">
-            <v>João Miranda</v>
-          </cell>
           <cell r="B307" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="308">
-          <cell r="A308" t="str">
-            <v>Gustavo Gentil</v>
-          </cell>
           <cell r="B308" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="309">
-          <cell r="A309" t="str">
-            <v>Sérgio Pereira</v>
-          </cell>
           <cell r="B309" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="310">
-          <cell r="A310" t="str">
-            <v>Fábio Cunha</v>
-          </cell>
           <cell r="B310" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="311">
-          <cell r="A311" t="str">
-            <v>Hugo Granja</v>
-          </cell>
           <cell r="B311" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="312">
-          <cell r="A312" t="str">
-            <v>João Palma</v>
-          </cell>
           <cell r="B312" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="313">
-          <cell r="A313" t="str">
-            <v>Tomás Paixão</v>
-          </cell>
           <cell r="B313" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="314">
-          <cell r="A314" t="str">
-            <v>Hugo Fora</v>
-          </cell>
           <cell r="B314" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="315">
-          <cell r="A315" t="str">
-            <v>Herman Politov</v>
-          </cell>
           <cell r="B315" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="316">
-          <cell r="A316" t="str">
-            <v>José Messejana</v>
-          </cell>
           <cell r="B316" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="317">
-          <cell r="A317" t="str">
-            <v>Nuno Gomes</v>
-          </cell>
           <cell r="B317" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="318">
-          <cell r="A318" t="str">
-            <v>Luis Pereira</v>
-          </cell>
           <cell r="B318" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="319">
-          <cell r="A319" t="str">
-            <v>Carlos Peixoto</v>
-          </cell>
           <cell r="B319" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="320">
-          <cell r="A320" t="str">
-            <v>Pedro Lopes</v>
-          </cell>
           <cell r="B320" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="321">
-          <cell r="A321" t="str">
-            <v>Tiago Avelino</v>
-          </cell>
           <cell r="B321" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="322">
-          <cell r="A322" t="str">
-            <v>Gustavo Baptista</v>
-          </cell>
           <cell r="B322" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="323">
-          <cell r="A323" t="str">
-            <v>Nuno Santos</v>
-          </cell>
           <cell r="B323" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="324">
-          <cell r="A324" t="str">
-            <v>Cláudio Câmara</v>
-          </cell>
           <cell r="B324" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="325">
-          <cell r="A325" t="str">
-            <v xml:space="preserve">Ricardo Rabeto </v>
-          </cell>
           <cell r="B325" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="326">
-          <cell r="A326" t="str">
-            <v>Tiago Ornelas</v>
-          </cell>
           <cell r="B326" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="327">
-          <cell r="A327" t="str">
-            <v>Sérgio Oliveira</v>
-          </cell>
           <cell r="B327" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="328">
-          <cell r="A328" t="str">
-            <v>Rúben Aguiar</v>
-          </cell>
           <cell r="B328" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="329">
-          <cell r="A329" t="str">
-            <v>Diogo Ornelas</v>
-          </cell>
           <cell r="B329" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="330">
-          <cell r="A330" t="str">
-            <v>Danilo Menezes</v>
-          </cell>
           <cell r="B330" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="331">
-          <cell r="A331" t="str">
-            <v>Gonçalo Cordeiro</v>
-          </cell>
           <cell r="B331" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="332">
-          <cell r="A332" t="str">
-            <v>Fillipe Velosa</v>
-          </cell>
           <cell r="B332" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="333">
-          <cell r="A333" t="str">
-            <v>Uriel Josen</v>
-          </cell>
           <cell r="B333" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="334">
-          <cell r="A334" t="str">
-            <v>André Leão</v>
-          </cell>
           <cell r="B334" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="335">
-          <cell r="A335" t="str">
-            <v>Miguel Beatriz</v>
-          </cell>
           <cell r="B335" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="336">
-          <cell r="A336" t="str">
-            <v>Diogo Chirondio</v>
-          </cell>
           <cell r="B336" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="337">
-          <cell r="A337" t="str">
-            <v>Diogo Grilo</v>
-          </cell>
           <cell r="B337" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="338">
-          <cell r="A338" t="str">
-            <v>Marco Duarte</v>
-          </cell>
           <cell r="B338" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="339">
-          <cell r="A339" t="str">
-            <v>Filipe Santo</v>
-          </cell>
           <cell r="B339" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="340">
-          <cell r="A340" t="str">
-            <v>José Mota</v>
-          </cell>
           <cell r="B340" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="341">
-          <cell r="A341" t="str">
-            <v>Marco Maurício</v>
-          </cell>
           <cell r="B341" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="342">
-          <cell r="A342" t="str">
-            <v>Pedro Filipe Costa</v>
-          </cell>
           <cell r="B342" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="343">
-          <cell r="A343" t="str">
-            <v>Ricardo Silva</v>
-          </cell>
           <cell r="B343" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="344">
-          <cell r="A344" t="str">
-            <v>Liliana Cruz</v>
-          </cell>
           <cell r="B344" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="345">
-          <cell r="A345" t="str">
-            <v>Sandra Andres</v>
-          </cell>
           <cell r="B345" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="346">
-          <cell r="A346" t="str">
-            <v>Mark Tunnicliffe</v>
-          </cell>
           <cell r="B346" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="347">
-          <cell r="A347" t="str">
-            <v>Asadi Muguro</v>
-          </cell>
           <cell r="B347" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="348">
-          <cell r="A348" t="str">
-            <v>Samira Benegal</v>
-          </cell>
           <cell r="B348" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="349">
-          <cell r="A349" t="str">
-            <v>Harmeet Singh</v>
-          </cell>
           <cell r="B349" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="350">
-          <cell r="A350" t="str">
-            <v>Olivier Priozeau</v>
-          </cell>
           <cell r="B350" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="351">
-          <cell r="A351" t="str">
-            <v>Luciano Marisi</v>
-          </cell>
           <cell r="B351" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="352">
-          <cell r="A352" t="str">
-            <v>Kalaiselvi Subramaniyam</v>
-          </cell>
           <cell r="B352" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="353">
-          <cell r="A353" t="str">
-            <v>James Tang</v>
-          </cell>
           <cell r="B353" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="354">
-          <cell r="A354" t="str">
-            <v>Anusree Ravi</v>
-          </cell>
           <cell r="B354" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="355">
-          <cell r="A355" t="str">
-            <v>Sivaram Gogineni</v>
-          </cell>
           <cell r="B355" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="356">
-          <cell r="A356" t="str">
-            <v>Sunith Nair</v>
-          </cell>
           <cell r="B356" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="357">
-          <cell r="A357" t="str">
-            <v>David Shalom</v>
-          </cell>
           <cell r="B357" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="358">
-          <cell r="A358" t="str">
-            <v>Daniel Carrillo</v>
-          </cell>
           <cell r="B358" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="359">
-          <cell r="A359" t="str">
-            <v>Niharika Katta</v>
-          </cell>
           <cell r="B359" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="360">
-          <cell r="A360" t="str">
-            <v>Nur Gas</v>
-          </cell>
           <cell r="B360" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="361">
-          <cell r="A361" t="str">
-            <v>Antonia Barnes-Christian</v>
-          </cell>
           <cell r="B361" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="362">
-          <cell r="A362" t="str">
-            <v>Abdur-Rahim Ali</v>
-          </cell>
           <cell r="B362" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="363">
-          <cell r="A363" t="str">
-            <v>Blandine Rumeau</v>
-          </cell>
           <cell r="B363" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="364">
-          <cell r="A364" t="str">
-            <v>Michal Dylka</v>
-          </cell>
           <cell r="B364" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="365">
-          <cell r="A365" t="str">
-            <v>Chris Nordberg</v>
-          </cell>
           <cell r="B365" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="366">
-          <cell r="A366" t="str">
-            <v>Joao Sousa</v>
-          </cell>
           <cell r="B366" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="367">
-          <cell r="A367" t="str">
-            <v>Tiago Martins</v>
-          </cell>
           <cell r="B367" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="368">
-          <cell r="A368" t="str">
-            <v>Volodymyr Nedashkivskyi</v>
-          </cell>
           <cell r="B368" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="369">
-          <cell r="A369" t="str">
-            <v>Eric Donovan</v>
-          </cell>
           <cell r="B369" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="370">
-          <cell r="A370" t="str">
-            <v>Matthew Fleischer</v>
-          </cell>
           <cell r="B370" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="371">
-          <cell r="A371" t="str">
-            <v>Pallavi Dughrekar</v>
-          </cell>
           <cell r="B371" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="372">
-          <cell r="A372" t="str">
-            <v>Blandine Rumeau</v>
-          </cell>
           <cell r="B372" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="373">
-          <cell r="A373" t="str">
-            <v>Volodymyr Nedashkivskyi</v>
-          </cell>
           <cell r="B373" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="374">
-          <cell r="A374" t="str">
-            <v>Viet Nguyen</v>
-          </cell>
           <cell r="B374" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="375">
-          <cell r="A375" t="str">
-            <v>Muhammad Aamir</v>
-          </cell>
           <cell r="B375" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="376">
-          <cell r="A376" t="str">
-            <v>Abdul Aziz Ibrahim Karim</v>
-          </cell>
           <cell r="B376" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="377">
-          <cell r="A377" t="str">
-            <v>Diogo Loureiro</v>
-          </cell>
           <cell r="B377" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="378">
-          <cell r="A378" t="str">
-            <v>Ana Oliveira</v>
-          </cell>
           <cell r="B378" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="379">
-          <cell r="A379" t="str">
-            <v>Marina Alves</v>
-          </cell>
           <cell r="B379" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="380">
-          <cell r="A380" t="str">
-            <v>Danilo Menezes</v>
-          </cell>
           <cell r="B380" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="381">
-          <cell r="A381" t="str">
-            <v>André Marques</v>
-          </cell>
           <cell r="B381" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="382">
-          <cell r="A382" t="str">
-            <v>Ricardo Monteiro</v>
-          </cell>
           <cell r="B382" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="383">
-          <cell r="A383" t="str">
-            <v>Václav Zůna</v>
-          </cell>
           <cell r="B383" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="384">
-          <cell r="A384" t="str">
-            <v>Diogo Loureiro</v>
-          </cell>
           <cell r="B384" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="385">
-          <cell r="A385" t="str">
-            <v>Ana Oliveira</v>
-          </cell>
           <cell r="B385" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="386">
-          <cell r="A386" t="str">
-            <v>Filipe Santo</v>
-          </cell>
           <cell r="B386" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="387">
-          <cell r="A387" t="str">
-            <v>Marina Alves</v>
-          </cell>
           <cell r="B387" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="388">
-          <cell r="A388" t="str">
-            <v>André Marques</v>
-          </cell>
           <cell r="B388" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="389">
-          <cell r="A389" t="str">
-            <v>Herman Politov</v>
-          </cell>
           <cell r="B389" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="390">
-          <cell r="A390" t="str">
-            <v>José Messejana</v>
-          </cell>
           <cell r="B390" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="391">
-          <cell r="A391" t="str">
-            <v>Nuno Gomes</v>
-          </cell>
           <cell r="B391" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="392">
-          <cell r="A392" t="str">
-            <v>Miguel Volkova</v>
-          </cell>
           <cell r="B392" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="393">
-          <cell r="A393" t="str">
-            <v>Ricardo Monteiro</v>
-          </cell>
           <cell r="B393" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="394">
-          <cell r="A394" t="str">
-            <v>Martin Petrus</v>
-          </cell>
           <cell r="B394" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="395">
-          <cell r="A395" t="str">
-            <v>Tomáš Kohout</v>
-          </cell>
           <cell r="B395" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="396">
-          <cell r="A396" t="str">
-            <v>David Aldorf</v>
-          </cell>
           <cell r="B396" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="397">
-          <cell r="A397" t="str">
-            <v>Alina Sedach</v>
-          </cell>
           <cell r="B397" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="398">
-          <cell r="A398" t="str">
-            <v>Jakub Sedlák</v>
-          </cell>
           <cell r="B398" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="399">
-          <cell r="A399" t="str">
-            <v>Michal Ursiny</v>
-          </cell>
           <cell r="B399" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="400">
-          <cell r="A400" t="str">
-            <v>Tomáš Král</v>
-          </cell>
           <cell r="B400" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="401">
-          <cell r="A401" t="str">
-            <v>Zdenek Obornik</v>
-          </cell>
           <cell r="B401" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="402">
-          <cell r="A402" t="str">
-            <v>Leopold Podmolík</v>
-          </cell>
           <cell r="B402" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="403">
-          <cell r="A403" t="str">
-            <v>Gabriela Mašková</v>
-          </cell>
           <cell r="B403" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="404">
-          <cell r="A404" t="str">
-            <v>Olga Tichánková</v>
-          </cell>
           <cell r="B404" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="405">
-          <cell r="A405" t="str">
-            <v>Antonín Safronov</v>
-          </cell>
           <cell r="B405" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="406">
-          <cell r="A406" t="str">
-            <v>Ana Correia</v>
-          </cell>
           <cell r="B406" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="407">
-          <cell r="A407" t="str">
-            <v>Marco Duarte</v>
-          </cell>
           <cell r="B407" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="408">
-          <cell r="A408" t="str">
-            <v>Geraldo Oliveira</v>
-          </cell>
           <cell r="B408" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="409">
-          <cell r="A409" t="str">
-            <v>Marcelo Antunes</v>
-          </cell>
           <cell r="B409" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="410">
-          <cell r="A410" t="str">
-            <v>Rui Roque</v>
-          </cell>
           <cell r="B410" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="411">
-          <cell r="A411" t="str">
-            <v>Ricardo Cardoso</v>
-          </cell>
           <cell r="B411" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="412">
-          <cell r="A412" t="str">
-            <v>Tiago Gomes</v>
-          </cell>
           <cell r="B412" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="413">
-          <cell r="A413" t="str">
-            <v>Andreia Catarrinho</v>
-          </cell>
           <cell r="B413" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="414">
-          <cell r="A414" t="str">
-            <v>Nuno Pereira</v>
-          </cell>
           <cell r="B414" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="415">
-          <cell r="A415" t="str">
-            <v>Miguel Franco</v>
-          </cell>
           <cell r="B415" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="416">
-          <cell r="A416" t="str">
-            <v>Francisco Faria Aleixo</v>
-          </cell>
           <cell r="B416" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="417">
-          <cell r="A417" t="str">
-            <v>Ricardo Carrapiço</v>
-          </cell>
           <cell r="B417" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="418">
-          <cell r="A418" t="str">
-            <v>João Silva</v>
-          </cell>
           <cell r="B418" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="419">
-          <cell r="A419" t="str">
-            <v>Ana Raquel Veríssimo</v>
-          </cell>
           <cell r="B419" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="420">
-          <cell r="A420" t="str">
-            <v>Nuno Rodrigues</v>
-          </cell>
           <cell r="B420" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="421">
-          <cell r="A421" t="str">
-            <v>Mário Quirino</v>
-          </cell>
           <cell r="B421" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="422">
-          <cell r="A422" t="str">
-            <v>André Souto</v>
-          </cell>
           <cell r="B422" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="423">
-          <cell r="A423" t="str">
-            <v>Bruno Filipe</v>
-          </cell>
           <cell r="B423" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="424">
-          <cell r="A424" t="str">
-            <v>Henrique Ferreira</v>
-          </cell>
           <cell r="B424" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="425">
-          <cell r="A425" t="str">
-            <v>Patric Venturini</v>
-          </cell>
           <cell r="B425" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="426">
-          <cell r="A426" t="str">
-            <v>Iago Cardoso</v>
-          </cell>
           <cell r="B426" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="427">
-          <cell r="A427" t="str">
-            <v>Joana Gomes</v>
-          </cell>
           <cell r="B427" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="428">
-          <cell r="A428" t="str">
-            <v>Martin Petrus</v>
-          </cell>
           <cell r="B428" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="429">
-          <cell r="A429" t="str">
-            <v>Alina Sedach</v>
-          </cell>
           <cell r="B429" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="430">
-          <cell r="A430" t="str">
-            <v>Jakub Sedlák</v>
-          </cell>
           <cell r="B430" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="431">
-          <cell r="A431" t="str">
-            <v>Zdenek Obornik</v>
-          </cell>
           <cell r="B431" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="432">
-          <cell r="A432" t="str">
-            <v>Leopold Podmolík</v>
-          </cell>
           <cell r="B432" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="433">
-          <cell r="A433" t="str">
-            <v>Olga Tichánková</v>
-          </cell>
           <cell r="B433" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="434">
-          <cell r="A434" t="str">
-            <v>Antonín Safronov</v>
-          </cell>
           <cell r="B434" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="435">
-          <cell r="A435" t="str">
-            <v>Sandra Ventura</v>
-          </cell>
           <cell r="B435" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="436">
-          <cell r="A436" t="str">
-            <v>Mhd Yhya Dabah</v>
-          </cell>
           <cell r="B436" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="437">
-          <cell r="A437" t="str">
-            <v>Miguel Volkova</v>
-          </cell>
           <cell r="B437" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="438">
-          <cell r="A438" t="str">
-            <v>Sandra Andres</v>
-          </cell>
           <cell r="B438" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="439">
-          <cell r="A439" t="str">
-            <v>Uriel Josen</v>
-          </cell>
           <cell r="B439" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="440">
-          <cell r="A440" t="str">
-            <v>Rita Franco</v>
-          </cell>
           <cell r="B440" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="441">
-          <cell r="A441" t="str">
-            <v>Joana Firmino</v>
-          </cell>
           <cell r="B441" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="442">
-          <cell r="A442" t="str">
-            <v>Crowdtesting</v>
-          </cell>
           <cell r="B442" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="443">
-          <cell r="A443" t="str">
-            <v>Crowdtesting</v>
-          </cell>
           <cell r="B443" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="444">
-          <cell r="A444" t="str">
-            <v>Crowdtesting</v>
-          </cell>
           <cell r="B444" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="445">
-          <cell r="A445" t="str">
-            <v>Crowdtesting</v>
-          </cell>
           <cell r="B445" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="446">
-          <cell r="A446" t="str">
-            <v>Anitha Lurdhusamy</v>
-          </cell>
           <cell r="B446" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="447">
-          <cell r="A447" t="str">
-            <v>João Bolinhas</v>
-          </cell>
           <cell r="B447" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="448">
-          <cell r="A448" t="str">
-            <v>Daniela Castro</v>
-          </cell>
           <cell r="B448" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="449">
-          <cell r="A449" t="str">
-            <v>Jan Špitálník</v>
-          </cell>
           <cell r="B449" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="450">
-          <cell r="A450" t="str">
-            <v>Diogo Santos</v>
-          </cell>
           <cell r="B450" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="451">
-          <cell r="A451" t="str">
-            <v>Duarte Miragaia</v>
-          </cell>
           <cell r="B451" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="452">
-          <cell r="A452" t="str">
-            <v>André Faria</v>
-          </cell>
           <cell r="B452" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="453">
-          <cell r="A453" t="str">
-            <v>João Cleto</v>
-          </cell>
           <cell r="B453" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="454">
-          <cell r="A454" t="str">
-            <v>Rita Rego</v>
-          </cell>
           <cell r="B454" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="455">
-          <cell r="A455" t="str">
-            <v>Tiago Jorge</v>
-          </cell>
           <cell r="B455" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="456">
-          <cell r="A456" t="str">
-            <v>Michael Mansfield</v>
-          </cell>
           <cell r="B456" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="457">
-          <cell r="A457" t="str">
-            <v>Ricardo Plácido</v>
-          </cell>
           <cell r="B457" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="458">
-          <cell r="A458" t="str">
-            <v>Eduardo Lopes</v>
-          </cell>
           <cell r="B458" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="459">
-          <cell r="A459" t="str">
-            <v>Sepandat Pourtaymour</v>
-          </cell>
           <cell r="B459" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="460">
-          <cell r="A460" t="str">
-            <v>Satya Peddireddi</v>
-          </cell>
           <cell r="B460" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="461">
-          <cell r="A461" t="str">
-            <v>Diego Di Mauro</v>
-          </cell>
           <cell r="B461" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="462">
-          <cell r="A462" t="str">
-            <v>Godwin Odenigbo</v>
-          </cell>
           <cell r="B462" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="463">
-          <cell r="A463" t="str">
-            <v>Tiago Goncalves Pereira</v>
-          </cell>
           <cell r="B463" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="464">
-          <cell r="A464" t="str">
-            <v>Ana Aires</v>
-          </cell>
           <cell r="B464" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="465">
-          <cell r="A465" t="str">
-            <v>João Caldeira</v>
-          </cell>
           <cell r="B465" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="466">
-          <cell r="A466" t="str">
-            <v>Diana Santos</v>
-          </cell>
           <cell r="B466" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="467">
-          <cell r="A467" t="str">
-            <v xml:space="preserve">Luis Matos </v>
-          </cell>
           <cell r="B467" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="468">
-          <cell r="A468" t="str">
-            <v xml:space="preserve">Paulo Fernando </v>
-          </cell>
           <cell r="B468" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="469">
-          <cell r="A469" t="str">
-            <v xml:space="preserve">Rita Gigante </v>
-          </cell>
           <cell r="B469" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="470">
-          <cell r="A470" t="str">
-            <v>David Martinez</v>
-          </cell>
           <cell r="B470" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="471">
-          <cell r="A471" t="str">
-            <v>Thomas Rands</v>
-          </cell>
           <cell r="B471" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="472">
-          <cell r="A472" t="str">
-            <v>Anthony Forte</v>
-          </cell>
           <cell r="B472" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="473">
-          <cell r="A473" t="str">
-            <v>Diogo Gonçalves</v>
-          </cell>
           <cell r="B473" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="474">
-          <cell r="A474" t="str">
-            <v>André Marrucho</v>
-          </cell>
           <cell r="B474" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="475">
-          <cell r="A475" t="str">
-            <v>Alfie Brooks</v>
-          </cell>
           <cell r="B475" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="476">
-          <cell r="A476" t="str">
-            <v>Gareth McKenna</v>
-          </cell>
           <cell r="B476" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="477">
-          <cell r="A477" t="str">
-            <v>Johann Martinache</v>
-          </cell>
           <cell r="B477" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="478">
-          <cell r="A478" t="str">
-            <v>Veronika Eve</v>
-          </cell>
           <cell r="B478" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="479">
-          <cell r="A479" t="str">
-            <v>Vinicius Campbell</v>
-          </cell>
           <cell r="B479" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="480">
-          <cell r="A480" t="str">
-            <v>Jorge Lourenço</v>
-          </cell>
           <cell r="B480" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="481">
-          <cell r="A481" t="str">
-            <v>Jorge Lourenço</v>
-          </cell>
           <cell r="B481" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="482">
-          <cell r="A482" t="str">
-            <v>Manuel Ferreira</v>
-          </cell>
           <cell r="B482" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="483">
-          <cell r="A483" t="str">
-            <v>Nelson Furtado</v>
-          </cell>
           <cell r="B483" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="484">
-          <cell r="A484" t="str">
-            <v>Paulo Costa</v>
-          </cell>
           <cell r="B484" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="485">
-          <cell r="A485" t="str">
-            <v>Luis Menezes</v>
-          </cell>
           <cell r="B485" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="486">
-          <cell r="A486" t="str">
-            <v>Nuno Jordão</v>
-          </cell>
           <cell r="B486" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="487">
-          <cell r="A487" t="str">
-            <v>Rodrigo Ferreira</v>
-          </cell>
           <cell r="B487" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="488">
-          <cell r="A488" t="str">
-            <v>Vivek Hesaraghatta</v>
-          </cell>
           <cell r="B488" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="489">
-          <cell r="A489" t="str">
-            <v>Arturo Garcia-Vargas</v>
-          </cell>
           <cell r="B489" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="490">
-          <cell r="A490" t="str">
-            <v>Laurie Poulter</v>
-          </cell>
           <cell r="B490" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="491">
-          <cell r="A491" t="str">
-            <v>Ramal Cooray</v>
-          </cell>
           <cell r="B491" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="492">
-          <cell r="A492" t="str">
-            <v>Josephine Fabricius</v>
-          </cell>
           <cell r="B492" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="493">
-          <cell r="A493" t="str">
-            <v>Pavithra Veerappa</v>
-          </cell>
           <cell r="B493" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="494">
-          <cell r="A494" t="str">
-            <v>Hugo Raimundo</v>
-          </cell>
           <cell r="B494" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="495">
-          <cell r="A495" t="str">
-            <v>Marlene Marques</v>
-          </cell>
           <cell r="B495" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="496">
-          <cell r="A496" t="str">
-            <v>João Martins</v>
-          </cell>
           <cell r="B496" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="497">
-          <cell r="A497" t="str">
-            <v>Susana Estevens</v>
-          </cell>
           <cell r="B497" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="498">
-          <cell r="A498" t="str">
-            <v>Joana Simões</v>
-          </cell>
           <cell r="B498" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="499">
-          <cell r="A499" t="str">
-            <v>Luísa Pimentel</v>
-          </cell>
           <cell r="B499" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="500">
-          <cell r="A500" t="str">
-            <v>Carla Coelho</v>
-          </cell>
           <cell r="B500" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="501">
-          <cell r="A501" t="str">
-            <v>Ivo Leitão</v>
-          </cell>
           <cell r="B501" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="502">
-          <cell r="A502" t="str">
-            <v>João Gonçalves</v>
-          </cell>
           <cell r="B502" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="503">
-          <cell r="A503" t="str">
-            <v>Sérgio Silva</v>
-          </cell>
           <cell r="B503" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="504">
-          <cell r="A504" t="str">
-            <v>Vítor Carvalho</v>
-          </cell>
           <cell r="B504" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="505">
-          <cell r="A505" t="str">
-            <v>Frederico Cerdeira</v>
-          </cell>
           <cell r="B505" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="506">
-          <cell r="A506" t="str">
-            <v>Yaser Al-Haidery</v>
-          </cell>
           <cell r="B506" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="507">
-          <cell r="A507" t="str">
-            <v>David White</v>
-          </cell>
           <cell r="B507" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="508">
-          <cell r="A508" t="str">
-            <v>Adam Greaves</v>
-          </cell>
           <cell r="B508" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="509">
-          <cell r="A509" t="str">
-            <v>Ashwini Vaidya</v>
-          </cell>
           <cell r="B509" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="510">
-          <cell r="A510" t="str">
-            <v>Tahir Mughal</v>
-          </cell>
           <cell r="B510" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="511">
-          <cell r="A511" t="str">
-            <v>Mrinalini Mohan</v>
-          </cell>
           <cell r="B511" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="512">
-          <cell r="A512" t="str">
-            <v>Kalpana Balasubramanianm</v>
-          </cell>
           <cell r="B512" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="513">
-          <cell r="A513" t="str">
-            <v>Grzegorz Szewczyk (Greg Chef)</v>
-          </cell>
           <cell r="B513" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="514">
-          <cell r="A514" t="str">
-            <v>João Travassos Martins</v>
-          </cell>
           <cell r="B514" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="515">
-          <cell r="A515" t="str">
-            <v>Mário Gonçalves</v>
-          </cell>
           <cell r="B515" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="516">
-          <cell r="A516" t="str">
-            <v>André Macedo</v>
-          </cell>
           <cell r="B516" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="517">
-          <cell r="A517" t="str">
-            <v>Laura McBride</v>
-          </cell>
           <cell r="B517" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="518">
-          <cell r="A518" t="str">
-            <v>Ricardo Serrão</v>
-          </cell>
           <cell r="B518" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="519">
-          <cell r="A519" t="str">
-            <v>Joao Furtado</v>
-          </cell>
           <cell r="B519" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="520">
-          <cell r="A520" t="str">
-            <v>Jamilson Junior</v>
-          </cell>
           <cell r="B520" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="521">
-          <cell r="A521" t="str">
-            <v>Pedro Cabral</v>
-          </cell>
           <cell r="B521" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="522">
-          <cell r="A522" t="str">
-            <v>João Saramago</v>
-          </cell>
           <cell r="B522" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="523">
-          <cell r="A523" t="str">
-            <v>Túlio Silva</v>
-          </cell>
           <cell r="B523" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="524">
-          <cell r="A524" t="str">
-            <v>Marcel Araujo</v>
-          </cell>
           <cell r="B524" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="525">
-          <cell r="A525" t="str">
-            <v>João Coelho</v>
-          </cell>
           <cell r="B525" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="526">
-          <cell r="A526" t="str">
-            <v>Bruno Silva</v>
-          </cell>
           <cell r="B526" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="527">
-          <cell r="A527" t="str">
-            <v>Beatriz Cabarrão</v>
-          </cell>
           <cell r="B527" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="528">
-          <cell r="A528" t="str">
-            <v>Danisha Gulamali</v>
-          </cell>
           <cell r="B528" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="529">
-          <cell r="A529" t="str">
-            <v>Nuno Nobre</v>
-          </cell>
           <cell r="B529" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="530">
-          <cell r="A530" t="str">
-            <v>Claudio Bartolomeu</v>
-          </cell>
           <cell r="B530" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="531">
-          <cell r="A531" t="str">
-            <v>Tiago Rosado</v>
-          </cell>
           <cell r="B531" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="532">
-          <cell r="A532" t="str">
-            <v>Rafael Carvalho</v>
-          </cell>
           <cell r="B532" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="533">
-          <cell r="A533" t="str">
-            <v>Henrique Vaz</v>
-          </cell>
           <cell r="B533" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="534">
-          <cell r="A534" t="str">
-            <v>Cássio Xavier</v>
-          </cell>
           <cell r="B534" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="535">
-          <cell r="A535" t="str">
-            <v>Carlos Florêncio</v>
-          </cell>
           <cell r="B535" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="536">
-          <cell r="A536" t="str">
-            <v>Pedro Barco</v>
-          </cell>
           <cell r="B536" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="537">
-          <cell r="A537" t="str">
-            <v>Nuno Pinto</v>
-          </cell>
           <cell r="B537" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="538">
-          <cell r="A538" t="str">
-            <v>Francisco Aguiar</v>
-          </cell>
           <cell r="B538" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="539">
-          <cell r="A539" t="str">
-            <v>José Reis</v>
-          </cell>
           <cell r="B539" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="540">
-          <cell r="A540" t="str">
-            <v>Catarina Guimaraes</v>
-          </cell>
           <cell r="B540" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="541">
-          <cell r="A541" t="str">
-            <v>Joana Soares</v>
-          </cell>
           <cell r="B541" t="str">
             <v>Discovery</v>
           </cell>
         </row>
         <row r="542">
-          <cell r="A542" t="str">
-            <v>Renata Martins</v>
-          </cell>
           <cell r="B542" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="543">
-          <cell r="A543" t="str">
-            <v>Jan Kufner</v>
-          </cell>
           <cell r="B543" t="str">
             <v>Experience</v>
           </cell>
         </row>
         <row r="544">
-          <cell r="A544" t="str">
-            <v>Patricia Rocha</v>
-          </cell>
           <cell r="B544" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="545">
-          <cell r="A545" t="str">
-            <v>Abdul Abdi</v>
-          </cell>
           <cell r="B545" t="str">
             <v>Commerce</v>
           </cell>
         </row>
         <row r="546">
-          <cell r="A546" t="str">
-            <v>Paulo Margaça</v>
-          </cell>
           <cell r="B546" t="str">
             <v>Tech</v>
           </cell>
         </row>
         <row r="547">
-          <cell r="A547" t="str">
-            <v>João Antunes</v>
-          </cell>
           <cell r="B547" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="548">
-          <cell r="A548" t="str">
-            <v>Marco Ferra</v>
-          </cell>
           <cell r="B548" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="549">
-          <cell r="A549" t="str">
-            <v>Johnathan Lucky</v>
-          </cell>
           <cell r="B549" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="550">
-          <cell r="A550" t="str">
-            <v>Faustino Silva</v>
-          </cell>
           <cell r="B550" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="551">
-          <cell r="A551" t="str">
-            <v>Sandro Carvalho</v>
-          </cell>
           <cell r="B551" t="str">
             <v>Shared</v>
           </cell>
         </row>
         <row r="552">
-          <cell r="A552" t="str">
-            <v>Bruno Gonçalves</v>
-          </cell>
           <cell r="B552" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="553">
-          <cell r="A553" t="str">
-            <v>Lúcio Lopes</v>
-          </cell>
           <cell r="B553" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="554">
-          <cell r="A554" t="str">
-            <v>Rebeca Bastos</v>
-          </cell>
           <cell r="B554" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="555">
-          <cell r="A555" t="str">
-            <v>Marc Gonçalves Nabais</v>
-          </cell>
           <cell r="B555" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="556">
-          <cell r="A556" t="str">
-            <v>Marius Morosan</v>
-          </cell>
           <cell r="B556" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="557">
-          <cell r="A557" t="str">
-            <v>Bryce Chamberlain</v>
-          </cell>
           <cell r="B557" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="558">
-          <cell r="A558" t="str">
-            <v>Ciara Smith</v>
-          </cell>
           <cell r="B558" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="559">
-          <cell r="A559" t="str">
-            <v>Cristal Rosado</v>
-          </cell>
           <cell r="B559" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="560">
-          <cell r="A560" t="str">
-            <v>Nilton Garcez</v>
-          </cell>
           <cell r="B560" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="561">
-          <cell r="A561" t="str">
-            <v>André Monteiro</v>
-          </cell>
           <cell r="B561" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="562">
-          <cell r="A562" t="str">
-            <v>Nuno Marcos</v>
-          </cell>
           <cell r="B562" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="563">
-          <cell r="A563" t="str">
-            <v>Ana Monteiro</v>
-          </cell>
           <cell r="B563" t="str">
             <v>Syndication</v>
           </cell>
         </row>
         <row r="564">
-          <cell r="A564" t="str">
-            <v>Keneth Jones</v>
-          </cell>
           <cell r="B564" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="565">
-          <cell r="A565" t="str">
-            <v>Rosaleen Boyce</v>
-          </cell>
           <cell r="B565" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="566">
-          <cell r="A566" t="str">
-            <v>Avtar Singh Dhami</v>
-          </cell>
           <cell r="B566" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="567">
-          <cell r="A567" t="str">
-            <v>Adam Greaves</v>
-          </cell>
           <cell r="B567" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="568">
-          <cell r="A568" t="str">
-            <v>Sasa Potiparski</v>
-          </cell>
           <cell r="B568" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="569">
-          <cell r="A569" t="str">
-            <v>Warren Margolin</v>
-          </cell>
           <cell r="B569" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="570">
-          <cell r="A570" t="str">
-            <v>Tahir Mughal</v>
-          </cell>
           <cell r="B570" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="571">
-          <cell r="A571" t="str">
-            <v>Nikephoros Petrou</v>
-          </cell>
           <cell r="B571" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="572">
-          <cell r="A572" t="str">
-            <v>Olajide Johnson</v>
-          </cell>
           <cell r="B572" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="573">
-          <cell r="A573" t="str">
-            <v>Meda Gradinar</v>
-          </cell>
           <cell r="B573" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="574">
-          <cell r="A574" t="str">
-            <v>Matthew Wilson</v>
-          </cell>
           <cell r="B574" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="575">
-          <cell r="A575" t="str">
-            <v>Bhupinder Bansal</v>
-          </cell>
           <cell r="B575" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="576">
-          <cell r="A576" t="str">
-            <v>Sinu Thomuas</v>
-          </cell>
           <cell r="B576" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="577">
-          <cell r="A577" t="str">
-            <v>Mrinalini Mohan</v>
-          </cell>
           <cell r="B577" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="578">
-          <cell r="A578" t="str">
-            <v>Kalpana Balasubramanianm</v>
-          </cell>
           <cell r="B578" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="579">
-          <cell r="A579" t="str">
-            <v>Grzegorz Szewczyk (Greg Chef)</v>
-          </cell>
           <cell r="B579" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="580">
-          <cell r="A580" t="str">
-            <v>Sajida Hashmi</v>
-          </cell>
           <cell r="B580" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="581">
-          <cell r="A581" t="str">
-            <v>Godfrey Otudeko</v>
-          </cell>
           <cell r="B581" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="582">
-          <cell r="A582" t="str">
-            <v>Yadevinder Gill</v>
-          </cell>
           <cell r="B582" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="583">
-          <cell r="A583" t="str">
-            <v>Jubair Jalil</v>
-          </cell>
           <cell r="B583" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="584">
-          <cell r="A584" t="str">
-            <v>Nikita Mehta</v>
-          </cell>
           <cell r="B584" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="585">
-          <cell r="A585" t="str">
-            <v>Ethan Dell</v>
-          </cell>
           <cell r="B585" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="586">
-          <cell r="A586" t="str">
-            <v>Jonathan Lee</v>
-          </cell>
           <cell r="B586" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="587">
-          <cell r="A587" t="str">
-            <v>Rete-Keyt Uibo</v>
-          </cell>
           <cell r="B587" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="588">
-          <cell r="A588" t="str">
-            <v>Mariam Basmajyan</v>
-          </cell>
           <cell r="B588" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="589">
-          <cell r="A589" t="str">
-            <v>Martin Pritchard</v>
-          </cell>
           <cell r="B589" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="590">
-          <cell r="A590" t="str">
-            <v>Sivaprakash Venkatesan</v>
-          </cell>
           <cell r="B590" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="591">
-          <cell r="A591" t="str">
-            <v>Sagara Dayananda</v>
-          </cell>
           <cell r="B591" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="592">
-          <cell r="A592" t="str">
-            <v>Margus Kiss</v>
-          </cell>
           <cell r="B592" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="593">
-          <cell r="A593" t="str">
-            <v>Raisha Shaik</v>
-          </cell>
           <cell r="B593" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="594">
-          <cell r="A594" t="str">
-            <v>Sunil Patel</v>
-          </cell>
           <cell r="B594" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="595">
-          <cell r="A595" t="str">
-            <v>Ming Liu</v>
-          </cell>
           <cell r="B595" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="596">
-          <cell r="A596" t="str">
-            <v>Lizz Ogunjimi</v>
-          </cell>
           <cell r="B596" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="597">
-          <cell r="A597" t="str">
-            <v>Prasad Lakmal</v>
-          </cell>
           <cell r="B597" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="598">
-          <cell r="A598" t="str">
-            <v>Fatima Al Ahmad</v>
-          </cell>
           <cell r="B598" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="599">
-          <cell r="A599" t="str">
-            <v>Oluwasegun Olumbe</v>
-          </cell>
           <cell r="B599" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="600">
-          <cell r="A600" t="str">
-            <v>Foumia Vallikulangara Khalid</v>
-          </cell>
           <cell r="B600" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="601">
-          <cell r="A601" t="str">
-            <v>Barry Bricknell</v>
-          </cell>
           <cell r="B601" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="602">
-          <cell r="A602" t="str">
-            <v>Bavan Samra</v>
-          </cell>
           <cell r="B602" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="603">
-          <cell r="A603" t="str">
-            <v>Tomas Rackauskas</v>
-          </cell>
           <cell r="B603" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="604">
-          <cell r="A604" t="str">
-            <v>Srujan Garisekurthi</v>
-          </cell>
           <cell r="B604" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="605">
-          <cell r="A605" t="str">
-            <v>Srinivasan Ramachandran</v>
-          </cell>
           <cell r="B605" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="606">
-          <cell r="A606" t="str">
-            <v>Nathan Saunders</v>
-          </cell>
           <cell r="B606" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="607">
-          <cell r="A607" t="str">
-            <v>Mohan Lella</v>
-          </cell>
           <cell r="B607" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="608">
-          <cell r="A608" t="str">
-            <v>Samantha Gildart</v>
-          </cell>
           <cell r="B608" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="609">
-          <cell r="A609" t="str">
-            <v>Reshma Shaik</v>
-          </cell>
           <cell r="B609" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="610">
-          <cell r="A610" t="str">
-            <v>Atikur Rahman</v>
-          </cell>
           <cell r="B610" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="611">
-          <cell r="A611" t="str">
-            <v>Ray Smith</v>
-          </cell>
           <cell r="B611" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="612">
-          <cell r="A612" t="str">
-            <v>Rao Guntupalli</v>
-          </cell>
           <cell r="B612" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="613">
-          <cell r="A613" t="str">
-            <v>Prashanti Munnangi</v>
-          </cell>
           <cell r="B613" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="614">
-          <cell r="A614" t="str">
-            <v>Vijayashree Kallimath</v>
-          </cell>
           <cell r="B614" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="615">
-          <cell r="A615" t="str">
-            <v>Desmond Hammond</v>
-          </cell>
           <cell r="B615" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="616">
-          <cell r="A616" t="str">
-            <v>Dominic Omordia</v>
-          </cell>
           <cell r="B616" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="617">
-          <cell r="A617" t="str">
-            <v>Adeniran Oniwinde</v>
-          </cell>
           <cell r="B617" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="618">
-          <cell r="A618" t="str">
-            <v>Raj Govindan</v>
-          </cell>
           <cell r="B618" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="619">
-          <cell r="A619" t="str">
-            <v>Rajeev Ranjan</v>
-          </cell>
           <cell r="B619" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="620">
-          <cell r="A620" t="str">
-            <v>Iva Vojinovic</v>
-          </cell>
           <cell r="B620" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="621">
-          <cell r="A621" t="str">
-            <v>Appaji Tholeti</v>
-          </cell>
           <cell r="B621" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="622">
-          <cell r="A622" t="str">
-            <v>Puneet Teng</v>
-          </cell>
           <cell r="B622" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="623">
-          <cell r="A623" t="str">
-            <v>Mark Carter</v>
-          </cell>
           <cell r="B623" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="624">
-          <cell r="A624" t="str">
-            <v>Thanh Huynh</v>
-          </cell>
           <cell r="B624" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="625">
-          <cell r="A625" t="str">
-            <v>Alistair  Priest</v>
-          </cell>
           <cell r="B625" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="626">
-          <cell r="A626" t="str">
-            <v>Simon Winton</v>
-          </cell>
           <cell r="B626" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="627">
-          <cell r="A627" t="str">
-            <v>Oliver Croysdill</v>
-          </cell>
           <cell r="B627" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="628">
-          <cell r="A628" t="str">
-            <v>Simon Rice</v>
-          </cell>
           <cell r="B628" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="629">
-          <cell r="A629" t="str">
-            <v>Usha Mannem</v>
-          </cell>
           <cell r="B629" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="630">
-          <cell r="A630" t="str">
-            <v>Priyank Shukla</v>
-          </cell>
           <cell r="B630" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="631">
-          <cell r="A631" t="str">
-            <v>Amad Dayekh</v>
-          </cell>
           <cell r="B631" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="632">
-          <cell r="A632" t="str">
-            <v>Sravan Bandela</v>
-          </cell>
           <cell r="B632" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="633">
-          <cell r="A633" t="str">
-            <v>Hermon Yohannes</v>
-          </cell>
           <cell r="B633" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="634">
-          <cell r="A634" t="str">
-            <v>James Gibbons</v>
-          </cell>
           <cell r="B634" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="635">
-          <cell r="A635" t="str">
-            <v>Bright Amankwaa</v>
-          </cell>
           <cell r="B635" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="636">
-          <cell r="A636" t="str">
-            <v>Brian Ainscough</v>
-          </cell>
           <cell r="B636" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="637">
-          <cell r="A637" t="str">
-            <v>Laurent Sebag</v>
-          </cell>
           <cell r="B637" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="638">
-          <cell r="A638" t="str">
-            <v>Ramiro Castro</v>
-          </cell>
           <cell r="B638" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="639">
-          <cell r="A639" t="str">
-            <v>Shravanya  Jerupothula</v>
-          </cell>
           <cell r="B639" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="640">
-          <cell r="A640" t="str">
-            <v>Pavani Gunna</v>
-          </cell>
           <cell r="B640" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="641">
-          <cell r="A641" t="str">
-            <v>Jaspal Bhogal</v>
-          </cell>
           <cell r="B641" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="642">
-          <cell r="A642" t="str">
-            <v>Deepa Yadav</v>
-          </cell>
           <cell r="B642" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="643">
-          <cell r="A643" t="str">
-            <v>Nicolas Kaayak</v>
-          </cell>
           <cell r="B643" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="644">
-          <cell r="A644" t="str">
-            <v>Alex Pal</v>
-          </cell>
           <cell r="B644" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="645">
-          <cell r="A645" t="str">
-            <v>Ali Galal</v>
-          </cell>
           <cell r="B645" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="646">
-          <cell r="A646" t="str">
-            <v>Radoslaw Zambrowski</v>
-          </cell>
           <cell r="B646" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="647">
-          <cell r="A647" t="str">
-            <v>John George</v>
-          </cell>
           <cell r="B647" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="648">
-          <cell r="A648" t="str">
-            <v>Thusyanthan Nathan</v>
-          </cell>
           <cell r="B648" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="649">
-          <cell r="A649" t="str">
-            <v>Dinesh Popli</v>
-          </cell>
           <cell r="B649" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="650">
-          <cell r="A650" t="str">
-            <v>Harsharani Shankamurthy</v>
-          </cell>
           <cell r="B650" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="651">
-          <cell r="A651" t="str">
-            <v>Pavan Prakash</v>
-          </cell>
           <cell r="B651" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="652">
-          <cell r="A652" t="str">
-            <v>Amair Ahmed</v>
-          </cell>
           <cell r="B652" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="653">
-          <cell r="A653" t="str">
-            <v>Akshay Khadse</v>
-          </cell>
           <cell r="B653" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="654">
-          <cell r="A654" t="str">
-            <v>Vijaya Koya</v>
-          </cell>
           <cell r="B654" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="655">
-          <cell r="A655" t="str">
-            <v>Ali Bayatpour</v>
-          </cell>
           <cell r="B655" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="656">
-          <cell r="A656" t="str">
-            <v>Adam Aasma</v>
-          </cell>
           <cell r="B656" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="657">
-          <cell r="A657" t="str">
-            <v>Oleksandra Tkalich</v>
-          </cell>
           <cell r="B657" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="658">
-          <cell r="A658" t="str">
-            <v>Dineth Basnayake</v>
-          </cell>
           <cell r="B658" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="659">
-          <cell r="A659" t="str">
-            <v>Tanuja Mulaparthi</v>
-          </cell>
           <cell r="B659" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="660">
-          <cell r="A660" t="str">
-            <v>Harshini Devadas</v>
-          </cell>
           <cell r="B660" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="661">
-          <cell r="A661" t="str">
-            <v>Krishnakumar Padmanabhan</v>
-          </cell>
           <cell r="B661" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="662">
-          <cell r="A662" t="str">
-            <v>Mukund Pritivatibayangram</v>
-          </cell>
           <cell r="B662" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="663">
-          <cell r="A663" t="str">
-            <v>Rakesh Pogaku</v>
-          </cell>
           <cell r="B663" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="664">
-          <cell r="A664" t="str">
-            <v>Caryappa Iynanda</v>
-          </cell>
           <cell r="B664" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="665">
-          <cell r="A665" t="str">
-            <v>Girish Babu</v>
-          </cell>
           <cell r="B665" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="666">
-          <cell r="A666" t="str">
-            <v>Santhosh Krishnan Nair</v>
-          </cell>
           <cell r="B666" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="667">
-          <cell r="A667" t="str">
-            <v>Swathi Maddineni</v>
-          </cell>
           <cell r="B667" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="668">
-          <cell r="A668" t="str">
-            <v>Bharat Kalra</v>
-          </cell>
           <cell r="B668" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="669">
-          <cell r="A669" t="str">
-            <v>Lynda Velu</v>
-          </cell>
           <cell r="B669" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="670">
-          <cell r="A670" t="str">
-            <v>Shwetha Budda</v>
-          </cell>
           <cell r="B670" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="671">
-          <cell r="A671" t="str">
-            <v>Vidya Poondi Santhanam</v>
-          </cell>
           <cell r="B671" t="str">
             <v>NOW</v>
           </cell>
         </row>
         <row r="672">
-          <cell r="A672" t="str">
-            <v>Maninder Massan</v>
-          </cell>
           <cell r="B672" t="str">
             <v>NOW</v>
           </cell>
@@ -7240,27 +5230,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8427D0-FED6-614E-81EC-B8F1D64D9635}">
   <dimension ref="A1:T75"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.125" customWidth="1"/>
-    <col min="9" max="9" width="61.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.08203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.08203125" customWidth="1"/>
+    <col min="9" max="9" width="61.08203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.08203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="25.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="25.5" customWidth="1"/>
     <col min="13" max="13" width="40.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23.5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="28" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="91.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.08203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="91.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -9359,15 +7349,6 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
     <Name>Document ID Generator</Name>
@@ -9416,9 +7397,48 @@
 </spe:Receivers>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a4b2985e-8075-4a13-89f9-6a14a0a360f6" ContentTypeId="0x0101000872A23329C4AC42A42DC877B8C5549E" PreviousValue="false"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <b61f0c131a914996ab71f79092e6263a xmlns="d9b316c9-70e1-43b4-89a2-fa0aab0c61d7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </b61f0c131a914996ab71f79092e6263a>
+    <TaxKeywordTaxHTField xmlns="8afd83c1-34ef-4475-95ec-b1400d36b782">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <g1accebf831647729c4d6deae28f9098 xmlns="d9b316c9-70e1-43b4-89a2-fa0aab0c61d7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </g1accebf831647729c4d6deae28f9098>
+    <TaxCatchAll xmlns="8afd83c1-34ef-4475-95ec-b1400d36b782" xsi:nil="true"/>
+    <e3321d89ea4a4cb692d83bbdf7d8626c xmlns="d9b316c9-70e1-43b4-89a2-fa0aab0c61d7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </e3321d89ea4a4cb692d83bbdf7d8626c>
+    <o1b54e17f42241ec9f9ce6cfc8d10dc8 xmlns="8afd83c1-34ef-4475-95ec-b1400d36b782">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </o1b54e17f42241ec9f9ce6cfc8d10dc8>
+    <NextReviewDate xmlns="d9b316c9-70e1-43b4-89a2-fa0aab0c61d7" xsi:nil="true"/>
+    <l16784b27bee415f80b87cdd8399701b xmlns="d9b316c9-70e1-43b4-89a2-fa0aab0c61d7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </l16784b27bee415f80b87cdd8399701b>
+    <hb5accf2246b4401a37370093a83748f xmlns="d9b316c9-70e1-43b4-89a2-fa0aab0c61d7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </hb5accf2246b4401a37370093a83748f>
+    <_dlc_DocId xmlns="8924654f-743d-4618-a7a6-903c1e33a7a9">TTAKFZKHN5RW-1484569472-78695</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="8924654f-743d-4618-a7a6-903c1e33a7a9">
+      <Url>https://universityofwestminster.sharepoint.com/sites/00380/_layouts/15/DocIdRedir.aspx?ID=TTAKFZKHN5RW-1484569472-78695</Url>
+      <Description>TTAKFZKHN5RW-1484569472-78695</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9663,56 +7683,62 @@
 </file>
 
 <file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <b61f0c131a914996ab71f79092e6263a xmlns="d9b316c9-70e1-43b4-89a2-fa0aab0c61d7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </b61f0c131a914996ab71f79092e6263a>
-    <TaxKeywordTaxHTField xmlns="8afd83c1-34ef-4475-95ec-b1400d36b782">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <g1accebf831647729c4d6deae28f9098 xmlns="d9b316c9-70e1-43b4-89a2-fa0aab0c61d7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </g1accebf831647729c4d6deae28f9098>
-    <TaxCatchAll xmlns="8afd83c1-34ef-4475-95ec-b1400d36b782" xsi:nil="true"/>
-    <e3321d89ea4a4cb692d83bbdf7d8626c xmlns="d9b316c9-70e1-43b4-89a2-fa0aab0c61d7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </e3321d89ea4a4cb692d83bbdf7d8626c>
-    <o1b54e17f42241ec9f9ce6cfc8d10dc8 xmlns="8afd83c1-34ef-4475-95ec-b1400d36b782">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </o1b54e17f42241ec9f9ce6cfc8d10dc8>
-    <NextReviewDate xmlns="d9b316c9-70e1-43b4-89a2-fa0aab0c61d7" xsi:nil="true"/>
-    <l16784b27bee415f80b87cdd8399701b xmlns="d9b316c9-70e1-43b4-89a2-fa0aab0c61d7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </l16784b27bee415f80b87cdd8399701b>
-    <hb5accf2246b4401a37370093a83748f xmlns="d9b316c9-70e1-43b4-89a2-fa0aab0c61d7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </hb5accf2246b4401a37370093a83748f>
-    <_dlc_DocId xmlns="8924654f-743d-4618-a7a6-903c1e33a7a9">TTAKFZKHN5RW-1484569472-78695</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="8924654f-743d-4618-a7a6-903c1e33a7a9">
-      <Url>https://universityofwestminster.sharepoint.com/sites/00380/_layouts/15/DocIdRedir.aspx?ID=TTAKFZKHN5RW-1484569472-78695</Url>
-      <Description>TTAKFZKHN5RW-1484569472-78695</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="a4b2985e-8075-4a13-89f9-6a14a0a360f6" ContentTypeId="0x0101000872A23329C4AC42A42DC877B8C5549E" PreviousValue="false"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF7806D6-A7D5-45C2-8B30-F38E36EA2F98}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D69EAF9-BA6F-4B0A-B98F-3AF0BB82A5FA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D69EAF9-BA6F-4B0A-B98F-3AF0BB82A5FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF7806D6-A7D5-45C2-8B30-F38E36EA2F98}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1873A3E-01D7-4931-88DB-3D38A8A87FCE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F8E1B7F-4ECE-4C2F-B476-D2DE65673F68}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d9b316c9-70e1-43b4-89a2-fa0aab0c61d7"/>
+    <ds:schemaRef ds:uri="8afd83c1-34ef-4475-95ec-b1400d36b782"/>
+    <ds:schemaRef ds:uri="8924654f-743d-4618-a7a6-903c1e33a7a9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36F28582-1463-4016-B82F-81C3168E0EC1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36F28582-1463-4016-B82F-81C3168E0EC1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8afd83c1-34ef-4475-95ec-b1400d36b782"/>
+    <ds:schemaRef ds:uri="d9b316c9-70e1-43b4-89a2-fa0aab0c61d7"/>
+    <ds:schemaRef ds:uri="8924654f-743d-4618-a7a6-903c1e33a7a9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F8E1B7F-4ECE-4C2F-B476-D2DE65673F68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1873A3E-01D7-4931-88DB-3D38A8A87FCE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>